--- a/data/trans_bre/P19C09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,43</t>
+          <t>-1,11; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,76</t>
+          <t>-1,4; 1,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,94</t>
+          <t>-3,34; 0,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 179,69</t>
+          <t>-28,75; 180,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 184,69</t>
+          <t>-57,95; 231,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,07; 54,21</t>
+          <t>-70,2; 52,69</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,57</t>
+          <t>-0,83; 2,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,04</t>
+          <t>0,24; 3,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,3</t>
+          <t>-1,02; 2,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 172,33</t>
+          <t>-26,14; 170,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 362,27</t>
+          <t>8,88; 347,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 125,6</t>
+          <t>-32,23; 120,21</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,86</t>
+          <t>-1,93; 1,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,84</t>
+          <t>-0,62; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,01</t>
+          <t>-3,55; -0,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 125,56</t>
+          <t>-52,32; 142,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 369,33</t>
+          <t>-34,52; 379,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,9; 11,57</t>
+          <t>-85,87; 15,49</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,79</t>
+          <t>-1,66; 1,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,93</t>
+          <t>-0,39; 3,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,44</t>
+          <t>-1,17; 2,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 115,94</t>
+          <t>-46,91; 93,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 194,36</t>
+          <t>-17,42; 204,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 115,67</t>
+          <t>-32,46; 116,63</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,46</t>
+          <t>-0,34; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,95</t>
+          <t>0,31; 1,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,66</t>
+          <t>-1,1; 0,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 68,66</t>
+          <t>-11,74; 69,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,85; 142,09</t>
+          <t>13,82; 140,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 27,7</t>
+          <t>-33,27; 29,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C09-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,55</t>
+          <t>-1,09; 3,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,78</t>
+          <t>-1,48; 1,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,83</t>
+          <t>-2,96; 1,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 180,31</t>
+          <t>-29,85; 186,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 231,4</t>
+          <t>-59,46; 191,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-70,2; 52,69</t>
+          <t>-68,88; 53,27</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,65</t>
+          <t>-0,76; 2,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,02</t>
+          <t>0,12; 3,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,18</t>
+          <t>-1,05; 2,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 170,74</t>
+          <t>-24,69; 202,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 347,08</t>
+          <t>-3,17; 334,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 120,21</t>
+          <t>-32,38; 111,52</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,97</t>
+          <t>-2,06; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,9</t>
+          <t>-0,72; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,06</t>
+          <t>-3,44; 0,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 142,3</t>
+          <t>-55,89; 115,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 379,01</t>
+          <t>-39,49; 359,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 15,49</t>
+          <t>-83,47; 17,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,65</t>
+          <t>-1,55; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,04</t>
+          <t>-0,45; 2,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,47</t>
+          <t>-1,16; 2,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 93,4</t>
+          <t>-45,38; 97,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 204,99</t>
+          <t>-16,45; 200,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 116,63</t>
+          <t>-33,81; 123,88</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,45</t>
+          <t>-0,35; 1,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,93</t>
+          <t>0,27; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,7</t>
+          <t>-1,05; 0,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 69,72</t>
+          <t>-11,64; 66,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,82; 140,94</t>
+          <t>12,43; 136,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 29,64</t>
+          <t>-32,54; 30,67</t>
         </is>
       </c>
     </row>
